--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Sheet 1 - Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet 4 - Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1 - Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 4 - Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -418,14 +418,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t>Holding Value Trend</a:t>
             </a:r>
@@ -443,14 +443,14 @@
             <v>JSW Steel</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -480,14 +480,14 @@
             <v>Coal India</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -517,14 +517,14 @@
             <v>Eternal</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -559,7 +559,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
@@ -583,7 +583,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
@@ -609,7 +609,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -624,9 +624,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -842,7 +842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -10238,13 +10238,13 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -10567,6 +10567,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$13</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$14</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$13</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$14</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$13</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$14</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$13</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$14</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$13</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$14</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$13</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$14</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1323,13 +1323,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="84" t="n"/>
-      <c r="B14" s="85" t="n"/>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="85" t="n"/>
-      <c r="E14" s="85" t="n"/>
-      <c r="F14" s="85" t="n"/>
-      <c r="G14" s="85" t="n"/>
+      <c r="A14" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>1268.6</v>
+      </c>
+      <c r="C14" s="19">
+        <f>B14*152</f>
+        <v/>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>414.7</v>
+      </c>
+      <c r="E14" s="19">
+        <f>D14*239</f>
+        <v/>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="G14" s="19">
+        <f>F14*313</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$14</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$15</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$14</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$15</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$14</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$15</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$14</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$15</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$14</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$15</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$14</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$15</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1349,13 +1349,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="84" t="n"/>
-      <c r="B15" s="85" t="n"/>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="85" t="n"/>
-      <c r="E15" s="85" t="n"/>
-      <c r="F15" s="85" t="n"/>
-      <c r="G15" s="85" t="n"/>
+      <c r="A15" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1267</v>
+      </c>
+      <c r="C15" s="19">
+        <f>B15*152</f>
+        <v/>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>428</v>
+      </c>
+      <c r="E15" s="19">
+        <f>D15*239</f>
+        <v/>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>342</v>
+      </c>
+      <c r="G15" s="19">
+        <f>F15*313</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$15</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$16</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$15</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$16</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$15</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$16</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$15</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$16</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$15</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$16</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$15</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$16</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1375,13 +1375,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="84" t="n"/>
-      <c r="B16" s="85" t="n"/>
-      <c r="C16" s="85" t="n"/>
-      <c r="D16" s="85" t="n"/>
-      <c r="E16" s="85" t="n"/>
-      <c r="F16" s="85" t="n"/>
-      <c r="G16" s="85" t="n"/>
+      <c r="A16" s="18" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1297.8</v>
+      </c>
+      <c r="C16" s="19">
+        <f>B16*152</f>
+        <v/>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>424.55</v>
+      </c>
+      <c r="E16" s="19">
+        <f>D16*239</f>
+        <v/>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="G16" s="19">
+        <f>F16*313</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$16</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$17</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$16</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$17</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$16</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$17</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$16</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$17</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$16</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$17</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$16</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$17</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1401,13 +1401,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="84" t="n"/>
-      <c r="B17" s="85" t="n"/>
-      <c r="C17" s="85" t="n"/>
-      <c r="D17" s="85" t="n"/>
-      <c r="E17" s="85" t="n"/>
-      <c r="F17" s="85" t="n"/>
-      <c r="G17" s="85" t="n"/>
+      <c r="A17" s="18" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>1273.2</v>
+      </c>
+      <c r="C17" s="19">
+        <f>B17*152</f>
+        <v/>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>422</v>
+      </c>
+      <c r="E17" s="19">
+        <f>D17*239</f>
+        <v/>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="G17" s="19">
+        <f>F17*313</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$17</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$18</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$17</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$18</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$17</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$18</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$17</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$18</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$17</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$18</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$17</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$18</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1427,13 +1427,30 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="n"/>
-      <c r="B18" s="85" t="n"/>
-      <c r="C18" s="85" t="n"/>
-      <c r="D18" s="85" t="n"/>
-      <c r="E18" s="85" t="n"/>
-      <c r="F18" s="85" t="n"/>
-      <c r="G18" s="85" t="n"/>
+      <c r="A18" s="18" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>1277</v>
+      </c>
+      <c r="C18" s="19">
+        <f>B18*152</f>
+        <v/>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>426.1</v>
+      </c>
+      <c r="E18" s="19">
+        <f>D18*239</f>
+        <v/>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>335</v>
+      </c>
+      <c r="G18" s="19">
+        <f>F18*313</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$18</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$19</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$18</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$19</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$18</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$19</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$18</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$19</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$18</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$19</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$18</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$19</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1453,13 +1453,30 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="84" t="n"/>
-      <c r="B19" s="85" t="n"/>
-      <c r="C19" s="85" t="n"/>
-      <c r="D19" s="85" t="n"/>
-      <c r="E19" s="85" t="n"/>
-      <c r="F19" s="85" t="n"/>
-      <c r="G19" s="85" t="n"/>
+      <c r="A19" s="18" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>1264.1</v>
+      </c>
+      <c r="C19" s="19">
+        <f>B19*152</f>
+        <v/>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>422.5</v>
+      </c>
+      <c r="E19" s="19">
+        <f>D19*239</f>
+        <v/>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="G19" s="19">
+        <f>F19*313</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$19</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$20</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$19</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$20</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$19</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$20</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$19</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$20</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$19</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$20</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$19</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$20</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1479,13 +1479,30 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="84" t="n"/>
-      <c r="B20" s="85" t="n"/>
-      <c r="C20" s="85" t="n"/>
-      <c r="D20" s="85" t="n"/>
-      <c r="E20" s="85" t="n"/>
-      <c r="F20" s="85" t="n"/>
-      <c r="G20" s="85" t="n"/>
+      <c r="A20" s="18" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>1272.4</v>
+      </c>
+      <c r="C20" s="19">
+        <f>B20*152</f>
+        <v/>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>425</v>
+      </c>
+      <c r="E20" s="19">
+        <f>D20*239</f>
+        <v/>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="G20" s="19">
+        <f>F20*313</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$20</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$21</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$20</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$21</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$20</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$21</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$20</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$21</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$20</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$21</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$20</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$21</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1505,13 +1505,30 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="84" t="n"/>
-      <c r="B21" s="85" t="n"/>
-      <c r="C21" s="85" t="n"/>
-      <c r="D21" s="85" t="n"/>
-      <c r="E21" s="85" t="n"/>
-      <c r="F21" s="85" t="n"/>
-      <c r="G21" s="85" t="n"/>
+      <c r="A21" s="18" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>1253.4</v>
+      </c>
+      <c r="C21" s="19">
+        <f>B21*152</f>
+        <v/>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>425</v>
+      </c>
+      <c r="E21" s="19">
+        <f>D21*239</f>
+        <v/>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>320</v>
+      </c>
+      <c r="G21" s="19">
+        <f>F21*313</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$21</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$22</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$21</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$22</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$21</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$22</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$21</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$22</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$21</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$22</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$21</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$22</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1531,13 +1531,30 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="84" t="n"/>
-      <c r="B22" s="85" t="n"/>
-      <c r="C22" s="85" t="n"/>
-      <c r="D22" s="85" t="n"/>
-      <c r="E22" s="85" t="n"/>
-      <c r="F22" s="85" t="n"/>
-      <c r="G22" s="85" t="n"/>
+      <c r="A22" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C22" s="19">
+        <f>B22*152</f>
+        <v/>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>420.4</v>
+      </c>
+      <c r="E22" s="19">
+        <f>D22*239</f>
+        <v/>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="G22" s="19">
+        <f>F22*313</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$22</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$23</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$22</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$23</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$22</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$23</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$22</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$23</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$22</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$23</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$22</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$23</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1557,13 +1557,30 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="84" t="n"/>
-      <c r="B23" s="85" t="n"/>
-      <c r="C23" s="85" t="n"/>
-      <c r="D23" s="85" t="n"/>
-      <c r="E23" s="85" t="n"/>
-      <c r="F23" s="85" t="n"/>
-      <c r="G23" s="85" t="n"/>
+      <c r="A23" s="18" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>1259.6</v>
+      </c>
+      <c r="C23" s="19">
+        <f>B23*152</f>
+        <v/>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>411.65</v>
+      </c>
+      <c r="E23" s="19">
+        <f>D23*239</f>
+        <v/>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>329</v>
+      </c>
+      <c r="G23" s="19">
+        <f>F23*313</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$23</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$24</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$23</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$24</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$23</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$24</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$23</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$24</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$23</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$24</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$23</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$24</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1583,13 +1583,30 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="84" t="n"/>
-      <c r="B24" s="85" t="n"/>
-      <c r="C24" s="85" t="n"/>
-      <c r="D24" s="85" t="n"/>
-      <c r="E24" s="85" t="n"/>
-      <c r="F24" s="85" t="n"/>
-      <c r="G24" s="85" t="n"/>
+      <c r="A24" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C24" s="19">
+        <f>B24*152</f>
+        <v/>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="E24" s="19">
+        <f>D24*239</f>
+        <v/>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>328</v>
+      </c>
+      <c r="G24" s="19">
+        <f>F24*313</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$24</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$25</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$24</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$25</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$24</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$25</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$24</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$25</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$24</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$25</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$24</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$25</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1609,13 +1609,30 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="84" t="n"/>
-      <c r="B25" s="85" t="n"/>
-      <c r="C25" s="85" t="n"/>
-      <c r="D25" s="85" t="n"/>
-      <c r="E25" s="85" t="n"/>
-      <c r="F25" s="85" t="n"/>
-      <c r="G25" s="85" t="n"/>
+      <c r="A25" s="18" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>1175.2</v>
+      </c>
+      <c r="C25" s="19">
+        <f>B25*152</f>
+        <v/>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="E25" s="19">
+        <f>D25*239</f>
+        <v/>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>319.05</v>
+      </c>
+      <c r="G25" s="19">
+        <f>F25*313</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$25</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$26</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$25</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$26</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$25</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$26</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$25</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$26</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$25</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$26</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$25</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$26</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1635,13 +1635,30 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="84" t="n"/>
-      <c r="B26" s="85" t="n"/>
-      <c r="C26" s="85" t="n"/>
-      <c r="D26" s="85" t="n"/>
-      <c r="E26" s="85" t="n"/>
-      <c r="F26" s="85" t="n"/>
-      <c r="G26" s="85" t="n"/>
+      <c r="A26" s="18" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>1168</v>
+      </c>
+      <c r="C26" s="19">
+        <f>B26*152</f>
+        <v/>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>411.55</v>
+      </c>
+      <c r="E26" s="19">
+        <f>D26*239</f>
+        <v/>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="G26" s="19">
+        <f>F26*313</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$26</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$27</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$26</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$27</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$26</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$27</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$26</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$27</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$26</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$27</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$26</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$27</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1661,13 +1661,30 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="84" t="n"/>
-      <c r="B27" s="85" t="n"/>
-      <c r="C27" s="85" t="n"/>
-      <c r="D27" s="85" t="n"/>
-      <c r="E27" s="85" t="n"/>
-      <c r="F27" s="85" t="n"/>
-      <c r="G27" s="85" t="n"/>
+      <c r="A27" s="18" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>1173</v>
+      </c>
+      <c r="C27" s="19">
+        <f>B27*152</f>
+        <v/>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>404.8</v>
+      </c>
+      <c r="E27" s="19">
+        <f>D27*239</f>
+        <v/>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>323</v>
+      </c>
+      <c r="G27" s="19">
+        <f>F27*313</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$27</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$28</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$27</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$28</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$27</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$28</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$27</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$28</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$27</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$28</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$27</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$28</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1687,13 +1687,30 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="84" t="n"/>
-      <c r="B28" s="85" t="n"/>
-      <c r="C28" s="85" t="n"/>
-      <c r="D28" s="85" t="n"/>
-      <c r="E28" s="85" t="n"/>
-      <c r="F28" s="85" t="n"/>
-      <c r="G28" s="85" t="n"/>
+      <c r="A28" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>1176.6</v>
+      </c>
+      <c r="C28" s="19">
+        <f>B28*152</f>
+        <v/>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="E28" s="19">
+        <f>D28*239</f>
+        <v/>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>320.45</v>
+      </c>
+      <c r="G28" s="19">
+        <f>F28*313</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$28</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$29</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$28</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$29</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$28</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$29</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$28</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$29</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$28</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$29</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$28</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$29</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1713,13 +1713,30 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="84" t="n"/>
-      <c r="B29" s="85" t="n"/>
-      <c r="C29" s="85" t="n"/>
-      <c r="D29" s="85" t="n"/>
-      <c r="E29" s="85" t="n"/>
-      <c r="F29" s="85" t="n"/>
-      <c r="G29" s="85" t="n"/>
+      <c r="A29" s="18" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>1176.2</v>
+      </c>
+      <c r="C29" s="19">
+        <f>B29*152</f>
+        <v/>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>417</v>
+      </c>
+      <c r="E29" s="19">
+        <f>D29*239</f>
+        <v/>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>316</v>
+      </c>
+      <c r="G29" s="19">
+        <f>F29*313</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$29</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$30</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$29</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$30</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$29</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$30</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$29</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$30</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$29</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$30</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$29</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$30</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1739,13 +1739,30 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="84" t="n"/>
-      <c r="B30" s="85" t="n"/>
-      <c r="C30" s="85" t="n"/>
-      <c r="D30" s="85" t="n"/>
-      <c r="E30" s="85" t="n"/>
-      <c r="F30" s="85" t="n"/>
-      <c r="G30" s="85" t="n"/>
+      <c r="A30" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>1200.4</v>
+      </c>
+      <c r="C30" s="19">
+        <f>B30*152</f>
+        <v/>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>418</v>
+      </c>
+      <c r="E30" s="19">
+        <f>D30*239</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>323</v>
+      </c>
+      <c r="G30" s="19">
+        <f>F30*313</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$30</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$31</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$30</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$31</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$30</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$31</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$30</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$31</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$30</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$31</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$30</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$31</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1765,13 +1765,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="84" t="n"/>
-      <c r="B31" s="85" t="n"/>
-      <c r="C31" s="85" t="n"/>
-      <c r="D31" s="85" t="n"/>
-      <c r="E31" s="85" t="n"/>
-      <c r="F31" s="85" t="n"/>
-      <c r="G31" s="85" t="n"/>
+      <c r="A31" s="18" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>1216.3</v>
+      </c>
+      <c r="C31" s="19">
+        <f>B31*152</f>
+        <v/>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>417.2</v>
+      </c>
+      <c r="E31" s="19">
+        <f>D31*239</f>
+        <v/>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="G31" s="19">
+        <f>F31*313</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$31</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$32</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$31</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$32</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$31</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$32</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$31</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$32</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$31</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$32</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$31</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$32</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1791,13 +1791,30 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="84" t="n"/>
-      <c r="B32" s="85" t="n"/>
-      <c r="C32" s="85" t="n"/>
-      <c r="D32" s="85" t="n"/>
-      <c r="E32" s="85" t="n"/>
-      <c r="F32" s="85" t="n"/>
-      <c r="G32" s="85" t="n"/>
+      <c r="A32" s="18" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>1241.3</v>
+      </c>
+      <c r="C32" s="19">
+        <f>B32*152</f>
+        <v/>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>411.7</v>
+      </c>
+      <c r="E32" s="19">
+        <f>D32*239</f>
+        <v/>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>320.2</v>
+      </c>
+      <c r="G32" s="19">
+        <f>F32*313</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$32</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$33</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$32</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$33</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$32</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$33</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$32</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$33</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$32</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$33</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$32</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$33</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1817,13 +1817,30 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="84" t="n"/>
-      <c r="B33" s="85" t="n"/>
-      <c r="C33" s="85" t="n"/>
-      <c r="D33" s="85" t="n"/>
-      <c r="E33" s="85" t="n"/>
-      <c r="F33" s="85" t="n"/>
-      <c r="G33" s="85" t="n"/>
+      <c r="A33" s="18" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="C33" s="19">
+        <f>B33*152</f>
+        <v/>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="E33" s="19">
+        <f>D33*239</f>
+        <v/>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="G33" s="19">
+        <f>F33*313</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$33</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$34</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$33</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$34</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$33</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$34</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$33</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$34</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$33</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$34</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$33</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$34</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1843,13 +1843,30 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="84" t="n"/>
-      <c r="B34" s="85" t="n"/>
-      <c r="C34" s="85" t="n"/>
-      <c r="D34" s="85" t="n"/>
-      <c r="E34" s="85" t="n"/>
-      <c r="F34" s="85" t="n"/>
-      <c r="G34" s="85" t="n"/>
+      <c r="A34" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C34" s="19">
+        <f>B34*152</f>
+        <v/>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="E34" s="19">
+        <f>D34*239</f>
+        <v/>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>304.45</v>
+      </c>
+      <c r="G34" s="19">
+        <f>F34*313</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$34</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$35</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$34</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$35</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$34</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$35</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$34</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$35</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$34</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$35</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$34</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$35</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1869,13 +1869,30 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="84" t="n"/>
-      <c r="B35" s="85" t="n"/>
-      <c r="C35" s="85" t="n"/>
-      <c r="D35" s="85" t="n"/>
-      <c r="E35" s="85" t="n"/>
-      <c r="F35" s="85" t="n"/>
-      <c r="G35" s="85" t="n"/>
+      <c r="A35" s="18" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>1185.5</v>
+      </c>
+      <c r="C35" s="19">
+        <f>B35*152</f>
+        <v/>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E35" s="19">
+        <f>D35*239</f>
+        <v/>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="G35" s="19">
+        <f>F35*313</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$35</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$36</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$35</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$36</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$35</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$36</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$35</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$36</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$35</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$36</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$35</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$36</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1895,13 +1895,30 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="84" t="n"/>
-      <c r="B36" s="85" t="n"/>
-      <c r="C36" s="85" t="n"/>
-      <c r="D36" s="85" t="n"/>
-      <c r="E36" s="85" t="n"/>
-      <c r="F36" s="85" t="n"/>
-      <c r="G36" s="85" t="n"/>
+      <c r="A36" s="18" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C36" s="19">
+        <f>B36*152</f>
+        <v/>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>405</v>
+      </c>
+      <c r="E36" s="19">
+        <f>D36*239</f>
+        <v/>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="G36" s="19">
+        <f>F36*313</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$36</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$37</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$36</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$37</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$36</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$37</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$36</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$37</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$36</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$37</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$36</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$37</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1921,13 +1921,30 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="84" t="n"/>
-      <c r="B37" s="85" t="n"/>
-      <c r="C37" s="85" t="n"/>
-      <c r="D37" s="85" t="n"/>
-      <c r="E37" s="85" t="n"/>
-      <c r="F37" s="85" t="n"/>
-      <c r="G37" s="85" t="n"/>
+      <c r="A37" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>1252.7</v>
+      </c>
+      <c r="C37" s="19">
+        <f>B37*152</f>
+        <v/>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>398</v>
+      </c>
+      <c r="E37" s="19">
+        <f>D37*239</f>
+        <v/>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>331</v>
+      </c>
+      <c r="G37" s="19">
+        <f>F37*313</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$37</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$38</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$37</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$38</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$37</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$38</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$37</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$38</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$37</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$38</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$37</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$38</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1947,13 +1947,30 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="84" t="n"/>
-      <c r="B38" s="85" t="n"/>
-      <c r="C38" s="85" t="n"/>
-      <c r="D38" s="85" t="n"/>
-      <c r="E38" s="85" t="n"/>
-      <c r="F38" s="85" t="n"/>
-      <c r="G38" s="85" t="n"/>
+      <c r="A38" s="18" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>1241.2</v>
+      </c>
+      <c r="C38" s="19">
+        <f>B38*152</f>
+        <v/>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>392</v>
+      </c>
+      <c r="E38" s="19">
+        <f>D38*239</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>326</v>
+      </c>
+      <c r="G38" s="19">
+        <f>F38*313</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$38</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$39</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$38</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$39</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$38</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$39</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$38</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$39</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$38</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$39</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$38</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$39</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1973,13 +1973,30 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="84" t="n"/>
-      <c r="B39" s="85" t="n"/>
-      <c r="C39" s="85" t="n"/>
-      <c r="D39" s="85" t="n"/>
-      <c r="E39" s="85" t="n"/>
-      <c r="F39" s="85" t="n"/>
-      <c r="G39" s="85" t="n"/>
+      <c r="A39" s="18" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>1255.4</v>
+      </c>
+      <c r="C39" s="19">
+        <f>B39*152</f>
+        <v/>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="E39" s="19">
+        <f>D39*239</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="G39" s="19">
+        <f>F39*313</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="84" t="n"/>

--- a/automated_stock_price_tracker.xlsx
+++ b/automated_stock_price_tracker.xlsx
@@ -457,7 +457,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$39</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$40</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -465,7 +465,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$C$2:$C$39</f>
+              <f>'Sheet 1 - Tracker'!$C$2:$C$40</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -494,7 +494,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$39</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$40</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -502,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$E$2:$E$39</f>
+              <f>'Sheet 1 - Tracker'!$E$2:$E$40</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -531,7 +531,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'Sheet 1 - Tracker'!$A$2:$A$39</f>
+              <f>'Sheet 1 - Tracker'!$A$2:$A$40</f>
               <strCache>
                 <ptCount val="0"/>
               </strCache>
@@ -539,7 +539,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Sheet 1 - Tracker'!$G$2:$G$39</f>
+              <f>'Sheet 1 - Tracker'!$G$2:$G$40</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="0"/>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable" displayName="TrackerTable" ref="A1:G40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="JSW Close"/>
@@ -1999,13 +1999,30 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="84" t="n"/>
-      <c r="B40" s="85" t="n"/>
-      <c r="C40" s="85" t="n"/>
-      <c r="D40" s="85" t="n"/>
-      <c r="E40" s="85" t="n"/>
-      <c r="F40" s="85" t="n"/>
-      <c r="G40" s="85" t="n"/>
+      <c r="A40" s="18" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>1246</v>
+      </c>
+      <c r="C40" s="19">
+        <f>B40*152</f>
+        <v/>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>389</v>
+      </c>
+      <c r="E40" s="19">
+        <f>D40*239</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="G40" s="19">
+        <f>F40*313</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="84" t="n"/>
